--- a/data/各工厂最大订单数.xlsx
+++ b/data/各工厂最大订单数.xlsx
@@ -110,7 +110,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Noto Sans CJK SC"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1107,73 +1107,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>540805</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>135725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>355745</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>117425</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6799580" y="6409055"/>
-          <a:ext cx="2200275" cy="349885"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202020204"/>
-              <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" sz="1600" dirty="0">
-            <a:solidFill>
-              <a:srgbClr val="808080">
-                <a:alpha val="19999"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:latin typeface="Arial" panose="020B0604020202020204"/>
-            <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1509,6 +1442,5 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>